--- a/doc/门店列表_v2.xlsx
+++ b/doc/门店列表_v2.xlsx
@@ -8,16 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Cursor\taobao_flashsale_monitor\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA367FBB-CC2E-41FF-9D4B-4CF57BDAB2F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96166B2F-C240-4FBC-B6A3-1D3C8FDDE2F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28470" yWindow="5805" windowWidth="25125" windowHeight="13590" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3146" yWindow="4920" windowWidth="23168" windowHeight="13594" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Input" sheetId="1" r:id="rId1"/>
     <sheet name="Input_All" sheetId="5" r:id="rId2"/>
-    <sheet name="门店名称汇总" sheetId="4" r:id="rId3"/>
-    <sheet name="Agent-WebHook" sheetId="2" r:id="rId4"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId5"/>
+    <sheet name="Agent-WebHook" sheetId="2" r:id="rId3"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId4"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -29,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="480" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="435" uniqueCount="71">
   <si>
     <t>https://qyapi.weixin.qq.com/cgi-bin/webhook/send?key=f882515e-aedc-4964-aba4-416b9c18b2f0</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -313,10 +312,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -619,733 +617,772 @@
   <dimension ref="A1:D85"/>
   <sheetFormatPr defaultRowHeight="14.15" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="48.7109375" style="4" customWidth="1"/>
-    <col min="2" max="2" width="14.85546875" style="4" customWidth="1"/>
-    <col min="3" max="3" width="18.7109375" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="38.78515625" style="4" customWidth="1"/>
+    <col min="1" max="1" width="69.640625" style="3" customWidth="1"/>
+    <col min="2" max="2" width="14.85546875" style="3" customWidth="1"/>
+    <col min="3" max="3" width="18.7109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="38.78515625" style="3" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="4" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="B2" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" s="6"/>
+      <c r="B2" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="5"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B3" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="D3" s="6"/>
+      <c r="B3" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="5"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B4" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="D4" s="6"/>
+      <c r="B4" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" s="5"/>
     </row>
     <row r="5" spans="1:4" ht="42.45" x14ac:dyDescent="0.35">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B5" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="D5" s="8" t="s">
+      <c r="B5" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D5" s="7" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A6" s="6" t="s">
+      <c r="A6" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B6" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="D6" s="6"/>
+      <c r="B6" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D6" s="5"/>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A7" s="6" t="s">
+      <c r="A7" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="D7" s="6"/>
+      <c r="B7" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D7" s="5"/>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A8" s="6"/>
-      <c r="B8" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="D8" s="6"/>
+      <c r="A8" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D8" s="5"/>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A9" s="6"/>
-      <c r="B9" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="D9" s="6"/>
+      <c r="A9" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D9" s="5"/>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A10" s="6"/>
-      <c r="B10" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="D10" s="6"/>
+      <c r="A10" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D10" s="5"/>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A11" s="6"/>
-      <c r="B11" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="D11" s="6"/>
+      <c r="A11" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D11" s="5"/>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A12" s="6"/>
-      <c r="B12" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="D12" s="6"/>
+      <c r="A12" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D12" s="5"/>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A13" s="6"/>
-      <c r="B13" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="D13" s="6"/>
+      <c r="A13" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D13" s="5"/>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B14" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C14" s="6" t="s">
+      <c r="A14" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C14" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B15" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="C15" s="6" t="s">
+      <c r="A15" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="C15" s="5" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B16" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C16" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="17" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B17" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C17" s="6" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="18" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B18" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="C18" s="6" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="19" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B19" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C19" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="20" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B20" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C20" s="6" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="21" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B21" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="C21" s="6" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="22" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B22" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C22" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="23" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B23" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C23" s="6" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="24" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B24" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="C24" s="6" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="25" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B25" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C25" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="26" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B26" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C26" s="6" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="27" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B27" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="C27" s="6" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="28" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B28" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C28" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="29" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B29" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C29" s="6" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="30" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B30" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="C30" s="6" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="31" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B31" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C31" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="32" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B32" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C32" s="6" t="s">
+      <c r="A16" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A17" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A18" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A19" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A20" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A21" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A22" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B23" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B24" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B25" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B26" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B27" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B28" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B29" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B30" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B31" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B32" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C32" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="33" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B33" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="C33" s="6" t="s">
+      <c r="B33" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="C33" s="5" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="34" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B34" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C34" s="6" t="s">
+      <c r="B34" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C34" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B35" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C35" s="6" t="s">
+      <c r="B35" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C35" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="36" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B36" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="C36" s="6" t="s">
+      <c r="B36" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="C36" s="5" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="37" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B37" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C37" s="6" t="s">
+      <c r="B37" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C37" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="38" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B38" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C38" s="6" t="s">
+      <c r="B38" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C38" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="39" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B39" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="C39" s="6" t="s">
+      <c r="B39" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="C39" s="5" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="40" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B40" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C40" s="6" t="s">
+      <c r="B40" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C40" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="41" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B41" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C41" s="6" t="s">
+      <c r="B41" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C41" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="42" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B42" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="C42" s="6" t="s">
+      <c r="B42" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="C42" s="5" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="43" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B43" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C43" s="6" t="s">
+      <c r="B43" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C43" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="44" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B44" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C44" s="6" t="s">
+      <c r="B44" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C44" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="45" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B45" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="C45" s="6" t="s">
+      <c r="B45" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="C45" s="5" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="46" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B46" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C46" s="6" t="s">
+      <c r="B46" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C46" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="47" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B47" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C47" s="6" t="s">
+      <c r="B47" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C47" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="48" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B48" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="C48" s="6" t="s">
+      <c r="B48" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="C48" s="5" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B49" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C49" s="6" t="s">
+      <c r="B49" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C49" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="50" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B50" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C50" s="6" t="s">
+      <c r="B50" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C50" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="51" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B51" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="C51" s="6" t="s">
+      <c r="B51" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="C51" s="5" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B52" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C52" s="6" t="s">
+      <c r="B52" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C52" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="53" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B53" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C53" s="6" t="s">
+      <c r="B53" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C53" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="54" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B54" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="C54" s="6" t="s">
+      <c r="B54" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="C54" s="5" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B55" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C55" s="6" t="s">
+      <c r="B55" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C55" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="56" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B56" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C56" s="6" t="s">
+      <c r="B56" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C56" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="57" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B57" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="C57" s="6" t="s">
+      <c r="B57" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="C57" s="5" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="58" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B58" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C58" s="6" t="s">
+      <c r="B58" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C58" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="59" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B59" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C59" s="6" t="s">
+      <c r="B59" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C59" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B60" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="C60" s="6" t="s">
+      <c r="B60" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="C60" s="5" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="61" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B61" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C61" s="6" t="s">
+      <c r="B61" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C61" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="62" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B62" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C62" s="6" t="s">
+      <c r="B62" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C62" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="63" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B63" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="C63" s="6" t="s">
+      <c r="B63" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="C63" s="5" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="64" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B64" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C64" s="6" t="s">
+      <c r="B64" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C64" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="65" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B65" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C65" s="6" t="s">
+      <c r="B65" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C65" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="66" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B66" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="C66" s="6" t="s">
+      <c r="B66" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="C66" s="5" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="67" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B67" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C67" s="6" t="s">
+      <c r="B67" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C67" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="68" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B68" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C68" s="6" t="s">
+      <c r="B68" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C68" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="69" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B69" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="C69" s="6" t="s">
+      <c r="B69" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="C69" s="5" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="70" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B70" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C70" s="6" t="s">
+      <c r="B70" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C70" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="71" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B71" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C71" s="6" t="s">
+      <c r="B71" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C71" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="72" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B72" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="C72" s="6" t="s">
+      <c r="B72" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="C72" s="5" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="73" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B73" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C73" s="6" t="s">
+      <c r="B73" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C73" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="74" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B74" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C74" s="6" t="s">
+      <c r="B74" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C74" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="75" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B75" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="C75" s="6" t="s">
+      <c r="B75" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="C75" s="5" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="76" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B76" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C76" s="6" t="s">
+      <c r="B76" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C76" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="77" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B77" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C77" s="6" t="s">
+      <c r="B77" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C77" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="78" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B78" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="C78" s="6" t="s">
+      <c r="B78" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="C78" s="5" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="79" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B79" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C79" s="6" t="s">
+      <c r="B79" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C79" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="80" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B80" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C80" s="6" t="s">
+      <c r="B80" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C80" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="81" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B81" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="C81" s="6" t="s">
+      <c r="B81" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="C81" s="5" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="82" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B82" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C82" s="6" t="s">
+      <c r="B82" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C82" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="83" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B83" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C83" s="6" t="s">
+      <c r="B83" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C83" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="84" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B84" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="C84" s="6" t="s">
+      <c r="B84" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="C84" s="5" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="85" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B85" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C85" s="6" t="s">
+      <c r="B85" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C85" s="5" t="s">
         <v>4</v>
       </c>
     </row>
@@ -1419,886 +1456,886 @@
   <dimension ref="A1:D85"/>
   <sheetFormatPr defaultRowHeight="14.15" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="69.640625" style="4" customWidth="1"/>
-    <col min="2" max="2" width="14.85546875" style="4" customWidth="1"/>
-    <col min="3" max="3" width="18.7109375" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="38.78515625" style="4" customWidth="1"/>
+    <col min="1" max="1" width="69.640625" style="3" customWidth="1"/>
+    <col min="2" max="2" width="14.85546875" style="3" customWidth="1"/>
+    <col min="3" max="3" width="18.7109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="38.78515625" style="3" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="4" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="B2" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" s="6"/>
+      <c r="B2" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="5"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B3" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="D3" s="6"/>
+      <c r="B3" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="5"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B4" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="D4" s="6"/>
+      <c r="B4" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" s="5"/>
     </row>
     <row r="5" spans="1:4" ht="42.45" x14ac:dyDescent="0.35">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B5" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="D5" s="8" t="s">
+      <c r="B5" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D5" s="7" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B6" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="D6" s="6"/>
+      <c r="B6" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D6" s="5"/>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="D7" s="6"/>
+      <c r="B7" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D7" s="5"/>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A8" s="4" t="s">
+      <c r="A8" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B8" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="D8" s="6"/>
+      <c r="B8" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D8" s="5"/>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A9" s="4" t="s">
+      <c r="A9" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B9" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="D9" s="6"/>
+      <c r="B9" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D9" s="5"/>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A10" s="4" t="s">
+      <c r="A10" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B10" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="D10" s="6"/>
+      <c r="B10" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D10" s="5"/>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A11" s="4" t="s">
+      <c r="A11" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B11" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="D11" s="6"/>
+      <c r="B11" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D11" s="5"/>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A12" s="4" t="s">
+      <c r="A12" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="D12" s="6"/>
+      <c r="B12" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D12" s="5"/>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A13" s="4" t="s">
+      <c r="A13" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="B13" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="D13" s="6"/>
+      <c r="B13" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D13" s="5"/>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A14" s="4" t="s">
+      <c r="A14" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B14" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C14" s="6" t="s">
+      <c r="B14" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C14" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A15" s="4" t="s">
+      <c r="A15" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="B15" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="C15" s="6" t="s">
+      <c r="B15" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="C15" s="5" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A16" s="4" t="s">
+      <c r="A16" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B16" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C16" s="6" t="s">
+      <c r="B16" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C16" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A17" s="4" t="s">
+      <c r="A17" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B17" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C17" s="6" t="s">
+      <c r="B17" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C17" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A18" s="4" t="s">
+      <c r="A18" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B18" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="C18" s="6" t="s">
+      <c r="B18" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="C18" s="5" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A19" s="4" t="s">
+      <c r="A19" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B19" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C19" s="6" t="s">
+      <c r="B19" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C19" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A20" s="4" t="s">
+      <c r="A20" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="B20" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C20" s="6" t="s">
+      <c r="B20" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C20" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A21" s="4" t="s">
+      <c r="A21" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B21" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="C21" s="6" t="s">
+      <c r="B21" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="C21" s="5" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A22" s="4" t="s">
+      <c r="A22" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B22" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C22" s="6" t="s">
+      <c r="B22" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C22" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A23" s="4" t="s">
+      <c r="A23" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B23" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C23" s="6" t="s">
+      <c r="B23" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C23" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A24" s="4" t="s">
+      <c r="A24" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B24" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="C24" s="6" t="s">
+      <c r="B24" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="C24" s="5" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A25" s="4" t="s">
+      <c r="A25" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B25" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C25" s="6" t="s">
+      <c r="B25" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C25" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A26" s="4" t="s">
+      <c r="A26" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="B26" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C26" s="6" t="s">
+      <c r="B26" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C26" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A27" s="4" t="s">
+      <c r="A27" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B27" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="C27" s="6" t="s">
+      <c r="B27" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="C27" s="5" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A28" s="4" t="s">
+      <c r="A28" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B28" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C28" s="6" t="s">
+      <c r="B28" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C28" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A29" s="4" t="s">
+      <c r="A29" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B29" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C29" s="6" t="s">
+      <c r="B29" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C29" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A30" s="4" t="s">
+      <c r="A30" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="B30" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="C30" s="6" t="s">
+      <c r="B30" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="C30" s="5" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A31" s="4" t="s">
+      <c r="A31" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B31" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C31" s="6" t="s">
+      <c r="B31" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C31" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A32" s="4" t="s">
+      <c r="A32" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="B32" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C32" s="6" t="s">
+      <c r="B32" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C32" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A33" s="4" t="s">
+      <c r="A33" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B33" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="C33" s="6" t="s">
+      <c r="B33" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="C33" s="5" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A34" s="4" t="s">
+      <c r="A34" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="B34" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C34" s="6" t="s">
+      <c r="B34" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C34" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A35" s="4" t="s">
+      <c r="A35" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B35" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C35" s="6" t="s">
+      <c r="B35" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C35" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A36" s="4" t="s">
+      <c r="A36" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="B36" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="C36" s="6" t="s">
+      <c r="B36" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="C36" s="5" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A37" s="4" t="s">
+      <c r="A37" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="B37" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C37" s="6" t="s">
+      <c r="B37" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C37" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A38" s="4" t="s">
+      <c r="A38" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B38" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C38" s="6" t="s">
+      <c r="B38" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C38" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A39" s="4" t="s">
+      <c r="A39" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="B39" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="C39" s="6" t="s">
+      <c r="B39" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="C39" s="5" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A40" s="4" t="s">
+      <c r="A40" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B40" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C40" s="6" t="s">
+      <c r="B40" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C40" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A41" s="4" t="s">
+      <c r="A41" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="B41" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C41" s="6" t="s">
+      <c r="B41" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C41" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A42" s="4" t="s">
+      <c r="A42" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B42" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="C42" s="6" t="s">
+      <c r="B42" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="C42" s="5" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A43" s="4" t="s">
+      <c r="A43" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="B43" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C43" s="6" t="s">
+      <c r="B43" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C43" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A44" s="4" t="s">
+      <c r="A44" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="B44" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C44" s="6" t="s">
+      <c r="B44" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C44" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A45" s="4" t="s">
+      <c r="A45" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="B45" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="C45" s="6" t="s">
+      <c r="B45" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="C45" s="5" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A46" s="4" t="s">
+      <c r="A46" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B46" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C46" s="6" t="s">
+      <c r="B46" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C46" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A47" s="4" t="s">
+      <c r="A47" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="B47" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C47" s="6" t="s">
+      <c r="B47" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C47" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A48" s="4" t="s">
+      <c r="A48" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B48" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="C48" s="6" t="s">
+      <c r="B48" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="C48" s="5" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A49" s="4" t="s">
+      <c r="A49" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="B49" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C49" s="6" t="s">
+      <c r="B49" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C49" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A50" s="4" t="s">
+      <c r="A50" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="B50" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C50" s="6" t="s">
+      <c r="B50" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C50" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A51" s="4" t="s">
+      <c r="A51" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="B51" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="C51" s="6" t="s">
+      <c r="B51" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="C51" s="5" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A52" s="4" t="s">
+      <c r="A52" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="B52" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C52" s="6" t="s">
+      <c r="B52" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C52" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A53" s="4" t="s">
+      <c r="A53" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="B53" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C53" s="6" t="s">
+      <c r="B53" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C53" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A54" s="4" t="s">
+      <c r="A54" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="B54" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="C54" s="6" t="s">
+      <c r="B54" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="C54" s="5" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A55" s="4" t="s">
+      <c r="A55" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="B55" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C55" s="6" t="s">
+      <c r="B55" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C55" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A56" s="4" t="s">
+      <c r="A56" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B56" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C56" s="6" t="s">
+      <c r="B56" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C56" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A57" s="4" t="s">
+      <c r="A57" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B57" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="C57" s="6" t="s">
+      <c r="B57" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="C57" s="5" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A58" s="4" t="s">
+      <c r="A58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B58" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C58" s="6" t="s">
+      <c r="B58" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C58" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A59" s="4" t="s">
+      <c r="A59" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B59" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C59" s="6" t="s">
+      <c r="B59" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C59" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A60" s="4" t="s">
+      <c r="A60" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B60" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="C60" s="6" t="s">
+      <c r="B60" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="C60" s="5" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B61" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C61" s="6" t="s">
+      <c r="B61" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C61" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B62" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C62" s="6" t="s">
+      <c r="B62" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C62" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B63" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="C63" s="6" t="s">
+      <c r="B63" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="C63" s="5" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B64" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C64" s="6" t="s">
+      <c r="B64" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C64" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="65" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B65" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C65" s="6" t="s">
+      <c r="B65" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C65" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="66" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B66" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="C66" s="6" t="s">
+      <c r="B66" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="C66" s="5" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="67" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B67" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C67" s="6" t="s">
+      <c r="B67" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C67" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="68" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B68" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C68" s="6" t="s">
+      <c r="B68" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C68" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="69" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B69" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="C69" s="6" t="s">
+      <c r="B69" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="C69" s="5" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="70" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B70" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C70" s="6" t="s">
+      <c r="B70" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C70" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="71" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B71" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C71" s="6" t="s">
+      <c r="B71" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C71" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="72" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B72" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="C72" s="6" t="s">
+      <c r="B72" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="C72" s="5" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="73" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B73" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C73" s="6" t="s">
+      <c r="B73" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C73" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="74" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B74" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C74" s="6" t="s">
+      <c r="B74" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C74" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="75" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B75" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="C75" s="6" t="s">
+      <c r="B75" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="C75" s="5" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="76" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B76" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C76" s="6" t="s">
+      <c r="B76" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C76" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="77" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B77" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C77" s="6" t="s">
+      <c r="B77" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C77" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="78" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B78" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="C78" s="6" t="s">
+      <c r="B78" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="C78" s="5" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="79" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B79" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C79" s="6" t="s">
+      <c r="B79" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C79" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="80" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B80" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C80" s="6" t="s">
+      <c r="B80" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C80" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="81" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B81" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="C81" s="6" t="s">
+      <c r="B81" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="C81" s="5" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="82" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B82" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C82" s="6" t="s">
+      <c r="B82" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C82" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="83" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B83" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C83" s="6" t="s">
+      <c r="B83" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C83" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="84" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B84" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="C84" s="6" t="s">
+      <c r="B84" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="C84" s="5" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="85" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B85" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C85" s="6" t="s">
+      <c r="B85" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C85" s="5" t="s">
         <v>4</v>
       </c>
     </row>
@@ -2368,323 +2405,6 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{58440698-2468-42CC-8A2C-100B784B34A3}">
-  <dimension ref="A1:A60"/>
-  <sheetFormatPr defaultRowHeight="14.15" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="69.640625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A1" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A15" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A16" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A17" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A18" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A19" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A20" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A21" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A22" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A23" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A24" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A25" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A26" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A27" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A28" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A29" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A30" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A31" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A32" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A33" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A34" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A35" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A36" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A37" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A38" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A39" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A40" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A41" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A42" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A43" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A44" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A45" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A46" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A47" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A48" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A49" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A50" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A51" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A52" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A53" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A54" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A55" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A56" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A57" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A58" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A59" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A60" t="s">
-        <v>31</v>
-      </c>
-    </row>
-  </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A1:A455">
-    <sortCondition descending="1" ref="A1:A455"/>
-  </sortState>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{389AD7A3-4A2A-4F47-8E87-5A2DE4654164}">
   <dimension ref="A2:C4"/>
   <sheetFormatPr defaultRowHeight="14.15" x14ac:dyDescent="0.35"/>
@@ -2736,7 +2456,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85216B65-0718-49EA-8FC0-DC486747A966}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.15" x14ac:dyDescent="0.35"/>
